--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_10d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_10d/close/close_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.0396984045792117</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.06282600541830785</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2655956232466137</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2199790178447225</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.2416918005653871</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.3495831566865811</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.3991485018444039</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.1841969563787921</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1751455362606977</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.2441705248832228</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>17.00720007920668</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2443604631823504</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.02425424187724545</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.2151866507222581</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1483159635189925</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.316483147450296</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.66794164301886</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.1619236275828777</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.268390861509055</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.141557059126428</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.9428745219539416</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>16.39179980585457</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.1298174973657629</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.01766431601602481</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.1926664123538844</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.1466152685858967</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.7324260422919663</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-0.9977197386600115</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>-0.06230924413294077</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.2442944247723329</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1224211318135456</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.551806275689728</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>17.21505668539572</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>0.03455762447360677</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.08430600650134168</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.2427283627132167</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0.1218559044003887</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.2035122427226709</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.343032820864862</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>-0.7259123145920261</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2439602674491458</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.1994531881079744</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>0.1476102669511913</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>17.6182489048077</v>
       </c>
     </row>
@@ -639,54 +747,90 @@
         <v>0.2883874383479303</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.05232872401696365</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.2246733468707938</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0.1199640509142378</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>1.216367840423586</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.744648389956458</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="I6" s="4" t="n">
+        <v>0.5348695263413497</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.1351986076102925</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.07686589760483675</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>2.222920066800131</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>18.47545174440321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1598221339153651</v>
+        <v>0.1605007584861762</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3325095652190794</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.9300112651284458</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.298624765296364</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1782229214048101</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3337111799482716</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.2000082814086596</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.9369006582233809</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.308249719636523</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.64482184682944</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.2019044494382929</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.527422612483861</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>16.42274801189298</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1137387120830333</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.546996430761035</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>16.4010559717098</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>